--- a/www/ig/fhir/core/StructureDefinition-fr-core-comment.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-comment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,7 +84,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>add a comment on a dataElement  of a resource | Ajout d'un commentaire sur un dataElement d'une ressource</t>
+    <t>Ajout d'un commentaire sur un dataElement d'une ressource.
+Add a comment on a dataElement  of a resource</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -132,7 +133,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>fhirpath:Patient.contact</t>
+    <t>element:Patient.contact</t>
   </si>
   <si>
     <t>ID</t>
@@ -259,7 +260,7 @@
 </t>
   </si>
   <si>
-    <t>Comment on a dataElement | Commentaire sur un dataElement</t>
+    <t>Comment on element Patient.contact | Commentaire sur l'élément Patient.contact</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -665,42 +666,42 @@
   <dimension ref="A1:AK6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.3515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.171875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="16.41796875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="16.41796875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="9.79296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="9.734375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="8.3984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="14.21484375" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="12.26171875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="19.80078125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="17.60546875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="17.4453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="17.08203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="15.18359375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="15.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="22.6796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="19.5625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/www/ig/fhir/core/StructureDefinition-fr-core-comment.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-comment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,8 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Ajout d'un commentaire sur un dataElement d'une ressource.
-Add a comment on a dataElement  of a resource</t>
+    <t>add a comment on a dataElement  of a resource | Ajout d'un commentaire sur un dataElement d'une ressource</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -115,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -133,7 +132,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:Patient.contact</t>
+    <t>fhirpath:Patient.contact</t>
   </si>
   <si>
     <t>ID</t>
@@ -260,7 +259,7 @@
 </t>
   </si>
   <si>
-    <t>Comment on element Patient.contact | Commentaire sur l'élément Patient.contact</t>
+    <t>Comment on a dataElement | Commentaire sur un dataElement</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -666,42 +665,42 @@
   <dimension ref="A1:AK6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="16.41796875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="16.41796875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="9.79296875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="7.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="19.03515625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="19.03515625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.3515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="8.171875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="8.3984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="9.734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="12.26171875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="14.21484375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="17.08203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="15.18359375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="15.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="19.80078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="17.60546875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="17.4453125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="19.5625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="22.6796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/www/ig/fhir/core/StructureDefinition-fr-core-comment.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-comment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,7 +84,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>add a comment on a dataElement  of a resource | Ajout d'un commentaire sur un dataElement d'une ressource</t>
+    <t>Ajout d'un commentaire sur un dataElement d'une ressource.
+Add a comment on a dataElement  of a resource</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -132,7 +133,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>fhirpath:Patient.contact</t>
+    <t>element:Patient.contact</t>
   </si>
   <si>
     <t>ID</t>
@@ -259,7 +260,7 @@
 </t>
   </si>
   <si>
-    <t>Comment on a dataElement | Commentaire sur un dataElement</t>
+    <t>Comment on element Patient.contact | Commentaire sur l'élément Patient.contact</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -665,42 +666,42 @@
   <dimension ref="A1:AK6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.3515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.171875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="16.41796875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="16.41796875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="9.79296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="9.734375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="8.3984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="14.21484375" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="12.26171875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="19.80078125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="17.60546875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="17.4453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="17.08203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="15.18359375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="15.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="22.6796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="19.5625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
